--- a/INFORME CLIENTE/ACUMULADO GENERAL.xlsx
+++ b/INFORME CLIENTE/ACUMULADO GENERAL.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7586,6 +7586,2757 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MISHELL ALEJANDRA HOYOS CIFUENTES</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1014292246</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AF29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW29" s="5">
+        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX29" s="5">
+        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY29" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" s="6">
+        <f>AW29/AY29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>AARON ALEJANDRO GALINDO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1233488618</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW30" s="5">
+        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX30" s="5">
+        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ30" s="6">
+        <f>AW30/AY30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>DILAN STIVEN SANCHEZ GAMEZ</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1057919701</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW31" s="5">
+        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX31" s="5">
+        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY31" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ31" s="6">
+        <f>AW31/AY31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>EMILIANA AVILES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1034788543</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW32" s="5">
+        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX32" s="5">
+        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ32" s="6">
+        <f>AW32/AY32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>JULIAN ESTEBAN ROJAS URREGO</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1025076168</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW33" s="5">
+        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX33" s="5">
+        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ33" s="6">
+        <f>AW33/AY33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NASHLY DANIELA BARRERA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1028877532</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW34" s="5">
+        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX34" s="5">
+        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ34" s="6">
+        <f>AW34/AY34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>EMMY SHANTHAL CABARCA MELO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1066097029</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW35" s="5">
+        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX35" s="5">
+        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ35" s="6">
+        <f>AW35/AY35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>DAFNE LUCIANA GARCIA PIAMBA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1141355418</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW36" s="5">
+        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX36" s="5">
+        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ36" s="6">
+        <f>AW36/AY36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NICOLAS STEBAN PALACIOS TIRADO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1233494561</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW37" s="5">
+        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX37" s="5">
+        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY37" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ37" s="6">
+        <f>AW37/AY37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>JOSEPH ALEJANDRO GONZALEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1025075979</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW38" s="5">
+        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX38" s="5">
+        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ38" s="6">
+        <f>AW38/AY38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>JUAN FELIPE PEDROZO AREVALO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1222209808</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW39" s="5">
+        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX39" s="5">
+        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY39" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ39" s="6">
+        <f>AW39/AY39</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7597,7 +10348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14632,6 +17383,2785 @@
       </c>
       <c r="AZ28" s="6">
         <f>AW28/AY28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MISHELL ALEJANDRA HOYOS CIFUENTES</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1014292246</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW29" s="5">
+        <f>COUNTIF(J29:AV29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX29" s="5">
+        <f>COUNTIF(J29:AV29,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY29" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ29" s="6">
+        <f>AW29/AY29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>AARON ALEJANDRO GALINDO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1233488618</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT30" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW30" s="5">
+        <f>COUNTIF(J30:AV30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX30" s="5">
+        <f>COUNTIF(J30:AV30,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ30" s="6">
+        <f>AW30/AY30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>DILAN STIVEN SANCHEZ GAMEZ</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1057919701</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW31" s="5">
+        <f>COUNTIF(J31:AV31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX31" s="5">
+        <f>COUNTIF(J31:AV31,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY31" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ31" s="6">
+        <f>AW31/AY31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>EMILIANA AVILES TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1034788543</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV32" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW32" s="5">
+        <f>COUNTIF(J32:AV32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX32" s="5">
+        <f>COUNTIF(J32:AV32,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ32" s="6">
+        <f>AW32/AY32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>JULIAN ESTEBAN ROJAS URREGO</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1025076168</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT33" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW33" s="5">
+        <f>COUNTIF(J33:AV33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX33" s="5">
+        <f>COUNTIF(J33:AV33,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ33" s="6">
+        <f>AW33/AY33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NASHLY DANIELA BARRERA ZAMBRANO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1028877532</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV34" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW34" s="5">
+        <f>COUNTIF(J34:AV34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX34" s="5">
+        <f>COUNTIF(J34:AV34,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY34" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ34" s="6">
+        <f>AW34/AY34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>EMMY SHANTHAL CABARCA MELO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1066097029</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT35" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AW35" s="5">
+        <f>COUNTIF(J35:AV35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX35" s="5">
+        <f>COUNTIF(J35:AV35,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY35" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ35" s="6">
+        <f>AW35/AY35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>DAFNE LUCIANA GARCIA PIAMBA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1141355418</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV36" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW36" s="5">
+        <f>COUNTIF(J36:AV36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX36" s="5">
+        <f>COUNTIF(J36:AV36,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY36" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ36" s="6">
+        <f>AW36/AY36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NICOLAS STEBAN PALACIOS TIRADO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1233494561</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AB37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV37" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW37" s="5">
+        <f>COUNTIF(J37:AV37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX37" s="5">
+        <f>COUNTIF(J37:AV37,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY37" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ37" s="6">
+        <f>AW37/AY37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>JOSEPH ALEJANDRO GONZALEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1025075979</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV38" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW38" s="5">
+        <f>COUNTIF(J38:AV38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX38" s="5">
+        <f>COUNTIF(J38:AV38,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY38" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ38" s="6">
+        <f>AW38/AY38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>111001800392</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO SOLEDAD ACOSTA DE SAMPER (IED) - SEDE PRINCIPAL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>JUAN FELIPE PEDROZO AREVALO</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1222209808</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>501</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW39" s="5">
+        <f>COUNTIF(J39:AV39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX39" s="5">
+        <f>COUNTIF(J39:AV39,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY39" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ39" s="6">
+        <f>AW39/AY39</f>
         <v/>
       </c>
     </row>

--- a/INFORME CLIENTE/ACUMULADO GENERAL.xlsx
+++ b/INFORME CLIENTE/ACUMULADO GENERAL.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10" yWindow="0" windowWidth="19190" windowHeight="10080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_MATEMÁTICAS" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_LENGUAJE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,7 +32,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -43,13 +42,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="FF9C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,17 +66,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,17 +90,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -129,7 +129,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -493,59 +493,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -848,17 +806,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>3</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -998,17 +959,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>6</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1148,17 +1112,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>9</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1298,17 +1265,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>5</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1448,17 +1418,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>5</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1598,17 +1571,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>11</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1748,17 +1724,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>11</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1898,17 +1877,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>11</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2048,17 +2030,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>14</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2198,17 +2183,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>7</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2348,17 +2336,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>12</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2498,17 +2489,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>9</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2648,17 +2642,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>8</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2798,17 +2795,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>8</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2948,17 +2948,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>7</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3098,17 +3101,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>14</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3248,17 +3254,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>7</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -3398,17 +3407,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>3</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3548,17 +3560,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>7</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3698,17 +3713,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>12</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -3848,17 +3866,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>7</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3998,17 +4019,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>6</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -4148,17 +4172,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>11</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -4298,17 +4325,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>5</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -4448,17 +4478,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>7</v>
+      <c r="AC26" s="5">
+        <f>COUNTIF(I26:AB26,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>COUNTIF(I26:AB26,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF26" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF26" s="6">
+        <f>AC26/AE26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -4598,17 +4631,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>10</v>
+      <c r="AC27" s="5">
+        <f>COUNTIF(I27:AB27,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>COUNTIF(I27:AB27,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF27" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF27" s="6">
+        <f>AC27/AE27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -4748,17 +4784,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>9</v>
+      <c r="AC28" s="5">
+        <f>COUNTIF(I28:AB28,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>COUNTIF(I28:AB28,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF28" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF28" s="6">
+        <f>AC28/AE28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -4898,17 +4937,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>16</v>
+      <c r="AC29" s="5">
+        <f>COUNTIF(I29:AB29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>COUNTIF(I29:AB29,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF29" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF29" s="6">
+        <f>AC29/AE29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -5048,17 +5090,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>10</v>
+      <c r="AC30" s="5">
+        <f>COUNTIF(I30:AB30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>COUNTIF(I30:AB30,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF30" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF30" s="6">
+        <f>AC30/AE30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -5198,17 +5243,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>7</v>
+      <c r="AC31" s="5">
+        <f>COUNTIF(I31:AB31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD31" s="5">
+        <f>COUNTIF(I31:AB31,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF31" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF31" s="6">
+        <f>AC31/AE31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -5348,17 +5396,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>12</v>
+      <c r="AC32" s="5">
+        <f>COUNTIF(I32:AB32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD32" s="5">
+        <f>COUNTIF(I32:AB32,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF32" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF32" s="6">
+        <f>AC32/AE32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -5498,17 +5549,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>9</v>
+      <c r="AC33" s="5">
+        <f>COUNTIF(I33:AB33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD33" s="5">
+        <f>COUNTIF(I33:AB33,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF33" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF33" s="6">
+        <f>AC33/AE33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -5648,17 +5702,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>8</v>
+      <c r="AC34" s="5">
+        <f>COUNTIF(I34:AB34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>COUNTIF(I34:AB34,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF34" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF34" s="6">
+        <f>AC34/AE34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -5798,17 +5855,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD35" s="5" t="n">
-        <v>8</v>
+      <c r="AC35" s="5">
+        <f>COUNTIF(I35:AB35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="5">
+        <f>COUNTIF(I35:AB35,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF35" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF35" s="6">
+        <f>AC35/AE35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -5948,17 +6008,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>8</v>
+      <c r="AC36" s="5">
+        <f>COUNTIF(I36:AB36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="5">
+        <f>COUNTIF(I36:AB36,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE36" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF36" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF36" s="6">
+        <f>AC36/AE36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -6098,17 +6161,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC37" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD37" s="5" t="n">
-        <v>13</v>
+      <c r="AC37" s="5">
+        <f>COUNTIF(I37:AB37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD37" s="5">
+        <f>COUNTIF(I37:AB37,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE37" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF37" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF37" s="6">
+        <f>AC37/AE37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -6248,17 +6314,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC38" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD38" s="5" t="n">
-        <v>8</v>
+      <c r="AC38" s="5">
+        <f>COUNTIF(I38:AB38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD38" s="5">
+        <f>COUNTIF(I38:AB38,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE38" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF38" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF38" s="6">
+        <f>AC38/AE38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6398,17 +6467,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC39" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD39" s="5" t="n">
-        <v>9</v>
+      <c r="AC39" s="5">
+        <f>COUNTIF(I39:AB39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD39" s="5">
+        <f>COUNTIF(I39:AB39,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE39" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF39" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF39" s="6">
+        <f>AC39/AE39</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6423,59 +6495,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -6778,17 +6808,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>1</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -6928,17 +6961,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>6</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -7078,17 +7114,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>12</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -7228,17 +7267,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>3</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -7378,17 +7420,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>5</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -7528,17 +7573,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>7</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -7678,17 +7726,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>5</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -7828,17 +7879,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>8</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -7978,17 +8032,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>13</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -8128,17 +8185,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>5</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -8278,17 +8338,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>7</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -8428,17 +8491,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>5</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -8578,17 +8644,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>4</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -8728,17 +8797,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>3</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -8878,17 +8950,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>4</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -9028,17 +9103,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>11</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -9178,17 +9256,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>6</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -9328,17 +9409,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>2</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -9478,17 +9562,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>4</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -9628,17 +9715,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>14</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -9778,17 +9868,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>5</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -9928,17 +10021,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>4</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -10078,17 +10174,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>6</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -10228,17 +10327,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>6</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -10378,17 +10480,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>5</v>
+      <c r="AC26" s="5">
+        <f>COUNTIF(I26:AB26,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>COUNTIF(I26:AB26,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF26" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF26" s="6">
+        <f>AC26/AE26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -10528,17 +10633,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>6</v>
+      <c r="AC27" s="5">
+        <f>COUNTIF(I27:AB27,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>COUNTIF(I27:AB27,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF27" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF27" s="6">
+        <f>AC27/AE27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -10678,17 +10786,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>2</v>
+      <c r="AC28" s="5">
+        <f>COUNTIF(I28:AB28,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>COUNTIF(I28:AB28,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF28" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF28" s="6">
+        <f>AC28/AE28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -10828,17 +10939,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>17</v>
+      <c r="AC29" s="5">
+        <f>COUNTIF(I29:AB29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>COUNTIF(I29:AB29,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF29" s="6" t="n">
-        <v>0.15</v>
+      <c r="AF29" s="6">
+        <f>AC29/AE29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -10978,17 +11092,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>6</v>
+      <c r="AC30" s="5">
+        <f>COUNTIF(I30:AB30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>COUNTIF(I30:AB30,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF30" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF30" s="6">
+        <f>AC30/AE30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -11128,17 +11245,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>4</v>
+      <c r="AC31" s="5">
+        <f>COUNTIF(I31:AB31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD31" s="5">
+        <f>COUNTIF(I31:AB31,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF31" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF31" s="6">
+        <f>AC31/AE31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -11278,17 +11398,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>8</v>
+      <c r="AC32" s="5">
+        <f>COUNTIF(I32:AB32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD32" s="5">
+        <f>COUNTIF(I32:AB32,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF32" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF32" s="6">
+        <f>AC32/AE32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -11428,17 +11551,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>8</v>
+      <c r="AC33" s="5">
+        <f>COUNTIF(I33:AB33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD33" s="5">
+        <f>COUNTIF(I33:AB33,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF33" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF33" s="6">
+        <f>AC33/AE33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -11578,17 +11704,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>4</v>
+      <c r="AC34" s="5">
+        <f>COUNTIF(I34:AB34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>COUNTIF(I34:AB34,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF34" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF34" s="6">
+        <f>AC34/AE34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -11728,17 +11857,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD35" s="5" t="n">
-        <v>4</v>
+      <c r="AC35" s="5">
+        <f>COUNTIF(I35:AB35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="5">
+        <f>COUNTIF(I35:AB35,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF35" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF35" s="6">
+        <f>AC35/AE35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -11878,17 +12010,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>5</v>
+      <c r="AC36" s="5">
+        <f>COUNTIF(I36:AB36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="5">
+        <f>COUNTIF(I36:AB36,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE36" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF36" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF36" s="6">
+        <f>AC36/AE36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -12028,17 +12163,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC37" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD37" s="5" t="n">
-        <v>4</v>
+      <c r="AC37" s="5">
+        <f>COUNTIF(I37:AB37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD37" s="5">
+        <f>COUNTIF(I37:AB37,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE37" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF37" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF37" s="6">
+        <f>AC37/AE37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -12178,17 +12316,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC38" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD38" s="5" t="n">
-        <v>8</v>
+      <c r="AC38" s="5">
+        <f>COUNTIF(I38:AB38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD38" s="5">
+        <f>COUNTIF(I38:AB38,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE38" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF38" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF38" s="6">
+        <f>AC38/AE38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -12328,17 +12469,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC39" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD39" s="5" t="n">
-        <v>5</v>
+      <c r="AC39" s="5">
+        <f>COUNTIF(I39:AB39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD39" s="5">
+        <f>COUNTIF(I39:AB39,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE39" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF39" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF39" s="6">
+        <f>AC39/AE39</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12353,59 +12497,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -12708,17 +12810,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>10</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -12858,17 +12963,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>8</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -13008,17 +13116,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>7</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -13158,17 +13269,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>5</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -13308,17 +13422,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>6</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -13458,17 +13575,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>4</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -13608,17 +13728,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>4</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -13758,17 +13881,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>11</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -13908,17 +14034,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>11</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -14058,17 +14187,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>9</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -14208,17 +14340,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>8</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -14358,17 +14493,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>15</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -14508,17 +14646,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>10</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -14658,17 +14799,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>9</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -14808,17 +14952,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>10</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -14958,17 +15105,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>13</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -15108,17 +15258,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>8</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -15258,17 +15411,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>5</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -15408,17 +15564,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>12</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -15558,17 +15717,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>6</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -15708,17 +15870,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>9</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -15858,17 +16023,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>16</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -16008,17 +16176,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>3</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -16158,17 +16329,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>3</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -16308,17 +16482,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>8</v>
+      <c r="AC26" s="5">
+        <f>COUNTIF(I26:AB26,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>COUNTIF(I26:AB26,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF26" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF26" s="6">
+        <f>AC26/AE26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -16458,17 +16635,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>6</v>
+      <c r="AC27" s="5">
+        <f>COUNTIF(I27:AB27,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>COUNTIF(I27:AB27,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF27" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF27" s="6">
+        <f>AC27/AE27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -16608,17 +16788,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>8</v>
+      <c r="AC28" s="5">
+        <f>COUNTIF(I28:AB28,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>COUNTIF(I28:AB28,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF28" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF28" s="6">
+        <f>AC28/AE28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -16758,17 +16941,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>6</v>
+      <c r="AC29" s="5">
+        <f>COUNTIF(I29:AB29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>COUNTIF(I29:AB29,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF29" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF29" s="6">
+        <f>AC29/AE29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -16908,17 +17094,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>7</v>
+      <c r="AC30" s="5">
+        <f>COUNTIF(I30:AB30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>COUNTIF(I30:AB30,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF30" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF30" s="6">
+        <f>AC30/AE30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -17058,17 +17247,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>7</v>
+      <c r="AC31" s="5">
+        <f>COUNTIF(I31:AB31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD31" s="5">
+        <f>COUNTIF(I31:AB31,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF31" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF31" s="6">
+        <f>AC31/AE31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -17208,17 +17400,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>7</v>
+      <c r="AC32" s="5">
+        <f>COUNTIF(I32:AB32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD32" s="5">
+        <f>COUNTIF(I32:AB32,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF32" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF32" s="6">
+        <f>AC32/AE32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -17358,17 +17553,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>6</v>
+      <c r="AC33" s="5">
+        <f>COUNTIF(I33:AB33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD33" s="5">
+        <f>COUNTIF(I33:AB33,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF33" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF33" s="6">
+        <f>AC33/AE33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -17508,17 +17706,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>10</v>
+      <c r="AC34" s="5">
+        <f>COUNTIF(I34:AB34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>COUNTIF(I34:AB34,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF34" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF34" s="6">
+        <f>AC34/AE34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -17658,17 +17859,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD35" s="5" t="n">
-        <v>5</v>
+      <c r="AC35" s="5">
+        <f>COUNTIF(I35:AB35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="5">
+        <f>COUNTIF(I35:AB35,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF35" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF35" s="6">
+        <f>AC35/AE35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -17808,17 +18012,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>5</v>
+      <c r="AC36" s="5">
+        <f>COUNTIF(I36:AB36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="5">
+        <f>COUNTIF(I36:AB36,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE36" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF36" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF36" s="6">
+        <f>AC36/AE36</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -17958,17 +18165,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC37" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD37" s="5" t="n">
-        <v>6</v>
+      <c r="AC37" s="5">
+        <f>COUNTIF(I37:AB37,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD37" s="5">
+        <f>COUNTIF(I37:AB37,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE37" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF37" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF37" s="6">
+        <f>AC37/AE37</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -18108,17 +18318,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC38" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD38" s="5" t="n">
-        <v>5</v>
+      <c r="AC38" s="5">
+        <f>COUNTIF(I38:AB38,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD38" s="5">
+        <f>COUNTIF(I38:AB38,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE38" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF38" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF38" s="6">
+        <f>AC38/AE38</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -18258,17 +18471,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC39" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD39" s="5" t="n">
-        <v>14</v>
+      <c r="AC39" s="5">
+        <f>COUNTIF(I39:AB39,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD39" s="5">
+        <f>COUNTIF(I39:AB39,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE39" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF39" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF39" s="6">
+        <f>AC39/AE39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -18408,17 +18624,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC40" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD40" s="5" t="n">
-        <v>14</v>
+      <c r="AC40" s="5">
+        <f>COUNTIF(I40:AB40,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD40" s="5">
+        <f>COUNTIF(I40:AB40,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE40" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF40" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF40" s="6">
+        <f>AC40/AE40</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -18433,59 +18652,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -18788,17 +18965,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>7</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -18938,17 +19118,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>3</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -19088,17 +19271,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>5</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -19238,17 +19424,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>2</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -19388,17 +19577,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>5</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -19538,17 +19730,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>3</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -19688,17 +19883,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>2</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -19838,17 +20036,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>0</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>1</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -19988,17 +20189,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>2</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -20138,17 +20342,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>5</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -20288,17 +20495,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>5</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -20438,17 +20648,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>1</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -20588,17 +20801,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>5</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -20738,17 +20954,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>1</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -20888,17 +21107,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>3</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -21038,17 +21260,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>4</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -21188,17 +21413,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>0</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>1</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -21338,17 +21566,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>11</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -21488,17 +21719,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>1</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -21638,17 +21872,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>0</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>1</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -21788,17 +22025,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>8</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -21938,17 +22178,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>8</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -22088,17 +22331,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>7</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -22238,17 +22484,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>1</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -22263,59 +22512,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -22618,17 +22825,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>9</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -22768,17 +22978,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>9</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -22918,17 +23131,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>9</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -23068,17 +23284,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>8</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -23218,17 +23437,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>9</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -23368,17 +23590,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>10</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -23518,17 +23743,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>13</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -23668,17 +23896,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>12</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -23818,17 +24049,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>15</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -23968,17 +24202,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>15</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -24118,17 +24355,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>10</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.5</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -24268,17 +24508,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>15</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -24418,17 +24661,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>13</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -24568,17 +24814,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>14</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -24718,17 +24967,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>12</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -24868,17 +25120,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>13</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -25018,17 +25273,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>13</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -25168,17 +25426,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>11</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -25318,17 +25579,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>16</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -25468,17 +25732,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>17</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>0.15</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -25618,17 +25885,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>16</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -25768,17 +26038,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>14</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -25918,17 +26191,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>11</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -26068,17 +26344,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>13</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -26218,17 +26497,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>15</v>
+      <c r="AC26" s="5">
+        <f>COUNTIF(I26:AB26,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>COUNTIF(I26:AB26,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF26" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF26" s="6">
+        <f>AC26/AE26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -26368,17 +26650,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>8</v>
+      <c r="AC27" s="5">
+        <f>COUNTIF(I27:AB27,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>COUNTIF(I27:AB27,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF27" s="6" t="n">
-        <v>0.6</v>
+      <c r="AF27" s="6">
+        <f>AC27/AE27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -26518,17 +26803,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>14</v>
+      <c r="AC28" s="5">
+        <f>COUNTIF(I28:AB28,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>COUNTIF(I28:AB28,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF28" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF28" s="6">
+        <f>AC28/AE28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -26668,17 +26956,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>17</v>
+      <c r="AC29" s="5">
+        <f>COUNTIF(I29:AB29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>COUNTIF(I29:AB29,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF29" s="6" t="n">
-        <v>0.15</v>
+      <c r="AF29" s="6">
+        <f>AC29/AE29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -26818,17 +27109,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>16</v>
+      <c r="AC30" s="5">
+        <f>COUNTIF(I30:AB30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>COUNTIF(I30:AB30,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF30" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF30" s="6">
+        <f>AC30/AE30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -26968,17 +27262,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>16</v>
+      <c r="AC31" s="5">
+        <f>COUNTIF(I31:AB31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD31" s="5">
+        <f>COUNTIF(I31:AB31,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF31" s="6" t="n">
-        <v>0.2</v>
+      <c r="AF31" s="6">
+        <f>AC31/AE31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -27118,17 +27415,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>14</v>
+      <c r="AC32" s="5">
+        <f>COUNTIF(I32:AB32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD32" s="5">
+        <f>COUNTIF(I32:AB32,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF32" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF32" s="6">
+        <f>AC32/AE32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -27268,17 +27568,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>12</v>
+      <c r="AC33" s="5">
+        <f>COUNTIF(I33:AB33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD33" s="5">
+        <f>COUNTIF(I33:AB33,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF33" s="6" t="n">
-        <v>0.4</v>
+      <c r="AF33" s="6">
+        <f>AC33/AE33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -27418,17 +27721,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>15</v>
+      <c r="AC34" s="5">
+        <f>COUNTIF(I34:AB34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>COUNTIF(I34:AB34,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF34" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF34" s="6">
+        <f>AC34/AE34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -27568,17 +27874,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD35" s="5" t="n">
-        <v>14</v>
+      <c r="AC35" s="5">
+        <f>COUNTIF(I35:AB35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="5">
+        <f>COUNTIF(I35:AB35,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF35" s="6" t="n">
-        <v>0.3</v>
+      <c r="AF35" s="6">
+        <f>AC35/AE35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -27718,17 +28027,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>15</v>
+      <c r="AC36" s="5">
+        <f>COUNTIF(I36:AB36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="5">
+        <f>COUNTIF(I36:AB36,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE36" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF36" s="6" t="n">
-        <v>0.25</v>
+      <c r="AF36" s="6">
+        <f>AC36/AE36</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -27743,59 +28055,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AF36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="12" customWidth="1" min="49" max="49"/>
-    <col width="12" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="9" max="48"/>
+    <col width="12" customWidth="1" min="49" max="51"/>
     <col width="18" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -28098,17 +28368,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC2" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD2" s="5" t="n">
-        <v>3</v>
+      <c r="AC2" s="5">
+        <f>COUNTIF(I2:AB2,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD2" s="5">
+        <f>COUNTIF(I2:AB2,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE2" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF2" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF2" s="6">
+        <f>AC2/AE2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -28248,17 +28521,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC3" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>1</v>
+      <c r="AC3" s="5">
+        <f>COUNTIF(I3:AB3,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD3" s="5">
+        <f>COUNTIF(I3:AB3,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE3" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF3" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF3" s="6">
+        <f>AC3/AE3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -28398,17 +28674,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>9</v>
+      <c r="AC4" s="5">
+        <f>COUNTIF(I4:AB4,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD4" s="5">
+        <f>COUNTIF(I4:AB4,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF4" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF4" s="6">
+        <f>AC4/AE4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -28548,17 +28827,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>13</v>
+      <c r="AC5" s="5">
+        <f>COUNTIF(I5:AB5,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD5" s="5">
+        <f>COUNTIF(I5:AB5,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE5" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF5" s="6" t="n">
-        <v>0.35</v>
+      <c r="AF5" s="6">
+        <f>AC5/AE5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -28698,17 +28980,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>17</v>
+      <c r="AC6" s="5">
+        <f>COUNTIF(I6:AB6,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD6" s="5">
+        <f>COUNTIF(I6:AB6,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF6" s="6" t="n">
-        <v>0.15</v>
+      <c r="AF6" s="6">
+        <f>AC6/AE6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -28848,17 +29133,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>9</v>
+      <c r="AC7" s="5">
+        <f>COUNTIF(I7:AB7,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD7" s="5">
+        <f>COUNTIF(I7:AB7,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF7" s="6" t="n">
-        <v>0.55</v>
+      <c r="AF7" s="6">
+        <f>AC7/AE7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -28998,17 +29286,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>2</v>
+      <c r="AC8" s="5">
+        <f>COUNTIF(I8:AB8,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD8" s="5">
+        <f>COUNTIF(I8:AB8,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF8" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF8" s="6">
+        <f>AC8/AE8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -29148,17 +29439,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>1</v>
+      <c r="AC9" s="5">
+        <f>COUNTIF(I9:AB9,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD9" s="5">
+        <f>COUNTIF(I9:AB9,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF9" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF9" s="6">
+        <f>AC9/AE9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -29298,17 +29592,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>3</v>
+      <c r="AC10" s="5">
+        <f>COUNTIF(I10:AB10,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="5">
+        <f>COUNTIF(I10:AB10,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF10" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF10" s="6">
+        <f>AC10/AE10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -29448,17 +29745,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>2</v>
+      <c r="AC11" s="5">
+        <f>COUNTIF(I11:AB11,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD11" s="5">
+        <f>COUNTIF(I11:AB11,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF11" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF11" s="6">
+        <f>AC11/AE11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -29598,17 +29898,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>4</v>
+      <c r="AC12" s="5">
+        <f>COUNTIF(I12:AB12,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD12" s="5">
+        <f>COUNTIF(I12:AB12,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF12" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF12" s="6">
+        <f>AC12/AE12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -29748,17 +30051,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>2</v>
+      <c r="AC13" s="5">
+        <f>COUNTIF(I13:AB13,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD13" s="5">
+        <f>COUNTIF(I13:AB13,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF13" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF13" s="6">
+        <f>AC13/AE13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -29898,17 +30204,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>4</v>
+      <c r="AC14" s="5">
+        <f>COUNTIF(I14:AB14,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD14" s="5">
+        <f>COUNTIF(I14:AB14,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF14" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF14" s="6">
+        <f>AC14/AE14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -30048,17 +30357,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>2</v>
+      <c r="AC15" s="5">
+        <f>COUNTIF(I15:AB15,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD15" s="5">
+        <f>COUNTIF(I15:AB15,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE15" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF15" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF15" s="6">
+        <f>AC15/AE15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -30198,17 +30510,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>2</v>
+      <c r="AC16" s="5">
+        <f>COUNTIF(I16:AB16,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD16" s="5">
+        <f>COUNTIF(I16:AB16,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE16" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF16" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF16" s="6">
+        <f>AC16/AE16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -30348,17 +30663,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD17" s="5" t="n">
-        <v>1</v>
+      <c r="AC17" s="5">
+        <f>COUNTIF(I17:AB17,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD17" s="5">
+        <f>COUNTIF(I17:AB17,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF17" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF17" s="6">
+        <f>AC17/AE17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -30498,17 +30816,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>2</v>
+      <c r="AC18" s="5">
+        <f>COUNTIF(I18:AB18,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD18" s="5">
+        <f>COUNTIF(I18:AB18,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF18" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF18" s="6">
+        <f>AC18/AE18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -30648,17 +30969,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>5</v>
+      <c r="AC19" s="5">
+        <f>COUNTIF(I19:AB19,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD19" s="5">
+        <f>COUNTIF(I19:AB19,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE19" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF19" s="6" t="n">
-        <v>0.75</v>
+      <c r="AF19" s="6">
+        <f>AC19/AE19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -30798,17 +31122,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>6</v>
+      <c r="AC20" s="5">
+        <f>COUNTIF(I20:AB20,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD20" s="5">
+        <f>COUNTIF(I20:AB20,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE20" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF20" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF20" s="6">
+        <f>AC20/AE20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -30948,17 +31275,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>6</v>
+      <c r="AC21" s="5">
+        <f>COUNTIF(I21:AB21,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD21" s="5">
+        <f>COUNTIF(I21:AB21,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF21" s="6" t="n">
-        <v>0.7</v>
+      <c r="AF21" s="6">
+        <f>AC21/AE21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -31098,17 +31428,20 @@
           <t>INCORRECTO</t>
         </is>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>11</v>
+      <c r="AC22" s="5">
+        <f>COUNTIF(I22:AB22,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="5">
+        <f>COUNTIF(I22:AB22,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="6" t="n">
-        <v>0.45</v>
+      <c r="AF22" s="6">
+        <f>AC22/AE22</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -31248,17 +31581,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>1</v>
+      <c r="AC23" s="5">
+        <f>COUNTIF(I23:AB23,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="5">
+        <f>COUNTIF(I23:AB23,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE23" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF23" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF23" s="6">
+        <f>AC23/AE23</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -31398,17 +31734,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>4</v>
+      <c r="AC24" s="5">
+        <f>COUNTIF(I24:AB24,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD24" s="5">
+        <f>COUNTIF(I24:AB24,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF24" s="6">
+        <f>AC24/AE24</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -31548,17 +31887,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>1</v>
+      <c r="AC25" s="5">
+        <f>COUNTIF(I25:AB25,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD25" s="5">
+        <f>COUNTIF(I25:AB25,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF25" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF25" s="6">
+        <f>AC25/AE25</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -31698,17 +32040,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>2</v>
+      <c r="AC26" s="5">
+        <f>COUNTIF(I26:AB26,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD26" s="5">
+        <f>COUNTIF(I26:AB26,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE26" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF26" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF26" s="6">
+        <f>AC26/AE26</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -31848,17 +32193,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>1</v>
+      <c r="AC27" s="5">
+        <f>COUNTIF(I27:AB27,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD27" s="5">
+        <f>COUNTIF(I27:AB27,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE27" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF27" s="6" t="n">
-        <v>0.95</v>
+      <c r="AF27" s="6">
+        <f>AC27/AE27</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -31998,17 +32346,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>7</v>
+      <c r="AC28" s="5">
+        <f>COUNTIF(I28:AB28,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD28" s="5">
+        <f>COUNTIF(I28:AB28,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE28" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF28" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF28" s="6">
+        <f>AC28/AE28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -32148,17 +32499,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>4</v>
+      <c r="AC29" s="5">
+        <f>COUNTIF(I29:AB29,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD29" s="5">
+        <f>COUNTIF(I29:AB29,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE29" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF29" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF29" s="6">
+        <f>AC29/AE29</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -32298,17 +32652,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>7</v>
+      <c r="AC30" s="5">
+        <f>COUNTIF(I30:AB30,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD30" s="5">
+        <f>COUNTIF(I30:AB30,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE30" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF30" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF30" s="6">
+        <f>AC30/AE30</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -32448,17 +32805,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>4</v>
+      <c r="AC31" s="5">
+        <f>COUNTIF(I31:AB31,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD31" s="5">
+        <f>COUNTIF(I31:AB31,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF31" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF31" s="6">
+        <f>AC31/AE31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -32598,17 +32958,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>2</v>
+      <c r="AC32" s="5">
+        <f>COUNTIF(I32:AB32,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD32" s="5">
+        <f>COUNTIF(I32:AB32,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF32" s="6" t="n">
-        <v>0.9</v>
+      <c r="AF32" s="6">
+        <f>AC32/AE32</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -32748,17 +33111,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>4</v>
+      <c r="AC33" s="5">
+        <f>COUNTIF(I33:AB33,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD33" s="5">
+        <f>COUNTIF(I33:AB33,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF33" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF33" s="6">
+        <f>AC33/AE33</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -32898,17 +33264,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>7</v>
+      <c r="AC34" s="5">
+        <f>COUNTIF(I34:AB34,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>COUNTIF(I34:AB34,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF34" s="6" t="n">
-        <v>0.65</v>
+      <c r="AF34" s="6">
+        <f>AC34/AE34</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -33048,17 +33417,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD35" s="5" t="n">
-        <v>4</v>
+      <c r="AC35" s="5">
+        <f>COUNTIF(I35:AB35,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD35" s="5">
+        <f>COUNTIF(I35:AB35,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF35" s="6" t="n">
-        <v>0.8</v>
+      <c r="AF35" s="6">
+        <f>AC35/AE35</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -33198,17 +33570,20 @@
           <t>CORRECTO</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>3</v>
+      <c r="AC36" s="5">
+        <f>COUNTIF(I36:AB36,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AD36" s="5">
+        <f>COUNTIF(I36:AB36,"INCORRECTO")</f>
+        <v/>
       </c>
       <c r="AE36" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="AF36" s="6" t="n">
-        <v>0.85</v>
+      <c r="AF36" s="6">
+        <f>AC36/AE36</f>
+        <v/>
       </c>
     </row>
   </sheetData>
